--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
@@ -312,7 +312,7 @@
   </si>
   <si>
     <t xml:space="preserve">但是啊…「不归之森」对我来说实在太可怕了～。所以，冒险者啊…能不能陪我一起去呀～？
-诶呀呀，你肯定没问题的～。该怎么说呢…你看起来既强大又可靠，更重要的是总觉得和你一起冒险会特别开心呢～。
+哎呀呀，你肯定没问题的～。该怎么说呢…你看起来既强大又可靠，更重要的是总觉得和你一起冒险会特别开心呢～。
 报酬当然不会少哦～。人类世界罕有的珍贵树种怎么样～？</t>
   </si>
   <si>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="fairy_nanasu" sheetId="1" r:id="rId3"/>
+    <sheet name="fairy_nanasu" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -290,83 +290,6 @@
   </si>
   <si>
     <t xml:space="preserve">nextPhase</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">我是娜娜苏，是茄子妖精哦～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你有什么烦恼吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">交付轻储包。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦，你是冒险者吗？其实我有件事情想要麻烦你…愿意听听看吗～？
-最近那些来到斯普睿的冒险者之间啊，在流传着某个奈菲亚中沉睡着惊人宝藏的传闻哦～。据说那个宝藏呀，是个能把放进去的东西变轻的神奇背包呢！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你看我很瘦弱对吧？我在冒险的时候经常被行李的重量压到想哭呢～。如果能有这个包，肯定能去更远的地方了～。能遇见更多人，经历更多有趣的冒险～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是啊…「不归之森」对我来说实在太可怕了～。所以，冒险者啊…能不能陪我一起去呀～？
-哎呀呀，你肯定没问题的～。该怎么说呢…你看起来既强大又可靠，更重要的是总觉得和你一起冒险会特别开心呢～。
-报酬当然不会少哦～。人类世界罕有的珍贵树种怎么样～？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">接受委托（危险度相当于20层）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还是算了</t>
-  </si>
-  <si>
-    <t xml:space="preserve">是吗～如果改变主意，记得来找我哦～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真的吗？好开心呀～。那么就做好冒险准备，前往奈菲亚吧。｢不归之森｣就在这里的西北边哦～。
-希望没有被莱伊娜和珀伊娜抢先一步…咦…？啊，当我什么都没说～！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">噢噢～成功啦冒险者！真的，真的找到了『轻储包』！
-莱伊娜和珀伊娜这次都太认真了，我一个人肯定不行的。真的太感谢你啦～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">给，约定好的报酬～。是人类地界很难弄到的稀有树种哦～。 还额外加了好多茄子当作谢礼呢～。
-好希望以后还能跟你一起冒险啊。
-…到时候就用这个包塞满茄子开宴会吧～。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">咦？奇怪…怎么翅膀突然麻麻的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">嗯—？你终于来了啊，娜娜苏。但是太迟了！
-你是来找｢神奇的包｣的吧？快看这里，我已经拿到手了！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">为什么莱伊娜会在这里～？那是我要找的包包。快还给我！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">还？才不要呢。奈菲亚的宝物都是先到先得吧？想要的话，就自己来抢呀。你的那个同伴，看起来不是挺强的嘛。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">初次见面啊，冒险者？我是雷之妖精莱伊娜。被电麻了可别怪我哦！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…吵死了。莱伊娜，你害我们失去偷袭的机会了。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">诶，可是珀伊娜，直接杀掉多无聊呀？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对吧娜娜苏？我根本不在乎这个破包。其实我只是想…看你为难的表情而已。爱哭鬼娜娜苏喊着「不要嘛～」的样子最有趣了。所以呢……要我还你？才不呢！想抢的话尽管动手呀？来来来，放马过来，今天也把你电成烤茄子！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">白痴…要玩随你，莱伊娜。但敢妨碍我就杀了你。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">呜哇—珀伊娜还是这么可怕～！不过，看来会很有趣呢，冒险者，你会陪我们玩的吧？</t>
   </si>
 </sst>
 </file>
@@ -388,25 +311,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -427,7 +350,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -452,7 +375,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -461,94 +384,94 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -562,13 +485,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -744,26 +667,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
-    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
-    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -801,24 +724,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="12.8">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="13.8">
-      <c r="I8" s="1">
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I8" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -827,11 +750,8 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="9" ht="13.8">
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -844,7 +764,7 @@
       <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -853,11 +773,8 @@
       <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="L9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="10" ht="13.8">
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -867,7 +784,7 @@
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -876,11 +793,8 @@
       <c r="K10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="L10" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
@@ -888,23 +802,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" ht="12.8">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="12.8">
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" ht="74.6">
-      <c r="I19" s="1">
+    <row r="19" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I19" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -913,12 +827,9 @@
       <c r="K19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L19" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="20" ht="13.8">
-      <c r="I20" s="1">
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I20" s="1" t="n">
         <v>22</v>
       </c>
       <c r="J20" s="8" t="s">
@@ -927,12 +838,9 @@
       <c r="K20" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="L20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" ht="113.4">
-      <c r="I21" s="1">
+    </row>
+    <row r="21" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I21" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J21" s="3" t="s">
@@ -941,18 +849,15 @@
       <c r="K21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="L21" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" ht="12.8">
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -961,18 +866,15 @@
       <c r="K23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="L23" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" ht="12.8">
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -981,11 +883,8 @@
       <c r="K24" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" ht="12.8">
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>39</v>
       </c>
@@ -993,13 +892,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" ht="23.85">
-      <c r="I28" s="1">
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="5" t="s">
@@ -1008,21 +907,18 @@
       <c r="K28" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="L28" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" ht="12.8">
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" ht="12.8">
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E32" s="1" t="s">
         <v>44</v>
       </c>
@@ -1030,14 +926,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" ht="64.15">
-      <c r="I34" s="1">
+    <row r="34" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I34" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J34" s="5" t="s">
@@ -1046,11 +942,8 @@
       <c r="K34" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="L34" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" ht="13.8">
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
@@ -1060,18 +953,18 @@
       <c r="J35" s="5"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" ht="12.8">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" ht="57.45">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J41" s="5" t="s">
@@ -1080,11 +973,8 @@
       <c r="K41" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="L41" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E42" s="1" t="s">
         <v>54</v>
       </c>
@@ -1092,8 +982,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" ht="91">
-      <c r="I43" s="1">
+    <row r="43" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I43" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J43" s="12" t="s">
@@ -1102,21 +992,18 @@
       <c r="K43" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L43" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="44" ht="12.8">
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" ht="12.8">
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" ht="12.8">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E47" s="1" t="s">
         <v>58</v>
       </c>
@@ -1124,11 +1011,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" ht="12.8">
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="1">
+      <c r="I48" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -1137,15 +1024,12 @@
       <c r="K48" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="L48" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" ht="46.25">
+    </row>
+    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G49" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I49" s="1">
+      <c r="I49" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J49" s="3" t="s">
@@ -1154,15 +1038,12 @@
       <c r="K49" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="L49" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="50" ht="13.8">
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="1">
+      <c r="I50" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J50" s="8" t="s">
@@ -1171,15 +1052,12 @@
       <c r="K50" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="L50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" ht="13.8">
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G51" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I51" s="1">
+      <c r="I51" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J51" s="8" t="s">
@@ -1188,15 +1066,12 @@
       <c r="K51" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="L51" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="52" ht="23.85">
+    </row>
+    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G52" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I52" s="1">
+      <c r="I52" s="1" t="n">
         <v>16</v>
       </c>
       <c r="J52" s="3" t="s">
@@ -1205,15 +1080,12 @@
       <c r="K52" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="L52" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="53" ht="13.8">
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G53" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I53" s="1">
+      <c r="I53" s="1" t="n">
         <v>17</v>
       </c>
       <c r="J53" s="8" t="s">
@@ -1222,15 +1094,12 @@
       <c r="K53" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="L53" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="54" ht="13.8">
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G54" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I54" s="1" t="n">
         <v>18</v>
       </c>
       <c r="J54" s="8" t="s">
@@ -1239,15 +1108,12 @@
       <c r="K54" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="L54" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" ht="12.8">
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G55" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I55" s="1" t="n">
         <v>19</v>
       </c>
       <c r="J55" s="14" t="s">
@@ -1256,15 +1122,12 @@
       <c r="K55" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="L55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="56" ht="12.8">
+    </row>
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G56" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I56" s="1">
+      <c r="I56" s="1" t="n">
         <v>20</v>
       </c>
       <c r="J56" s="14" t="s">
@@ -1273,17 +1136,14 @@
       <c r="K56" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="L56" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" ht="12.8">
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E57" s="7"/>
       <c r="F57" s="15"/>
       <c r="G57" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I57" s="1">
+      <c r="I57" s="1" t="n">
         <v>21</v>
       </c>
       <c r="J57" s="14" t="s">
@@ -1292,14 +1152,11 @@
       <c r="K57" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="L57" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="58" ht="12.8">
+    </row>
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G58" s="11"/>
     </row>
-    <row r="59" ht="12.8">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E59" s="1" t="s">
         <v>58</v>
       </c>
@@ -1308,7 +1165,7 @@
       </c>
       <c r="G59" s="11"/>
     </row>
-    <row r="60" ht="12.8">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E60" s="1" t="s">
         <v>84</v>
       </c>
@@ -1317,19 +1174,19 @@
       </c>
       <c r="G60" s="11"/>
     </row>
-    <row r="61" ht="12.8">
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="1" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/fairy_nanasu.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="fairy_nanasu" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="fairy_nanasu" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="108">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -290,6 +290,83 @@
   </si>
   <si>
     <t xml:space="preserve">nextPhase</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">我是娜娜苏，是茄子妖精哦～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你有什么烦恼吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">交付轻储包。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咦，你是冒险者吗？其实我有件事情想要麻烦你…愿意听听看吗～？
+最近那些来到斯普睿的冒险者之间啊，在流传着某个奈菲亚中沉睡着惊人宝藏的传闻哦～。据说那个宝藏呀，是个能把放进去的东西变轻的神奇背包呢！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你看我很瘦弱对吧？我在冒险的时候经常被行李的重量压到想哭呢～。如果能有这个包，肯定能去更远的地方了～。能遇见更多人，经历更多有趣的冒险～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是啊…「不归之森」对我来说实在太可怕了～。所以，冒险者啊…能不能陪我一起去呀～？
+哎呀呀，你肯定没问题的～。该怎么说呢…你看起来既强大又可靠，更重要的是总觉得和你一起冒险会特别开心呢～。
+报酬当然不会少哦～。人类世界罕有的珍贵树种怎么样～？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">接受委托（危险度相当于20层）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还是算了</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是吗～如果改变主意，记得来找我哦～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真的吗？好开心呀～。那么就做好冒险准备，前往奈菲亚吧。｢不归之森｣就在这里的西北边哦～。
+希望没有被莱伊娜和珀伊娜抢先一步…咦…？啊，当我什么都没说～！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">噢噢～成功啦冒险者！真的，真的找到了『轻储包』！
+莱伊娜和珀伊娜这次都太认真了，我一个人肯定不行的。真的太感谢你啦～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">给，约定好的报酬～。是人类地界很难弄到的稀有树种哦～。 还额外加了好多茄子当作谢礼呢～。
+好希望以后还能跟你一起冒险啊。
+…到时候就用这个包塞满茄子开宴会吧～。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">咦？奇怪…怎么翅膀突然麻麻的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">嗯—？你终于来了啊，娜娜苏。但是太迟了！
+你是来找｢神奇的包｣的吧？快看这里，我已经拿到手了！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">为什么莱伊娜会在这里～？那是我要找的包包。快还给我！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">还？才不要呢。奈菲亚的宝物都是先到先得吧？想要的话，就自己来抢呀。你的那个同伴，看起来不是挺强的嘛。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">初次见面啊，冒险者？我是雷之妖精莱伊娜。被电麻了可别怪我哦！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…吵死了。莱伊娜，你害我们失去偷袭的机会了。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">诶，可是珀伊娜，直接杀掉多无聊呀？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对吧娜娜苏？我根本不在乎这个破包。其实我只是想…看你为难的表情而已。爱哭鬼娜娜苏喊着「不要嘛～」的样子最有趣了。所以呢……要我还你？才不呢！想抢的话尽管动手呀？来来来，放马过来，今天也把你电成烤茄子！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">白痴…要玩随你，莱伊娜。但敢妨碍我就杀了你。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">呜哇—珀伊娜还是这么可怕～！不过，看来会很有趣呢，冒险者，你会陪我们玩的吧？</t>
   </si>
 </sst>
 </file>
@@ -311,25 +388,25 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -350,7 +427,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -375,7 +452,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -384,94 +461,94 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -485,13 +562,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -667,26 +744,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L61"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="21.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="60.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="9.06"/>
+    <col min="1" max="1" width="8.85" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.28" style="1" customWidth="1"/>
+    <col min="4" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="60.76" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.06" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -724,24 +801,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" ht="12.8">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I8" s="1" t="n">
+    <row r="8" ht="13.8">
+      <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -750,8 +827,11 @@
       <c r="K8" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="9" ht="13.8">
       <c r="B9" s="1" t="s">
         <v>16</v>
       </c>
@@ -764,7 +844,7 @@
       <c r="E9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="I9" s="1">
         <v>2</v>
       </c>
       <c r="J9" s="5" t="s">
@@ -773,8 +853,11 @@
       <c r="K9" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="10" ht="13.8">
       <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
@@ -784,7 +867,7 @@
       <c r="E10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>3</v>
       </c>
       <c r="J10" s="5" t="s">
@@ -793,8 +876,11 @@
       <c r="K10" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="E11" s="1" t="s">
         <v>26</v>
       </c>
@@ -802,23 +888,23 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" ht="12.8">
       <c r="E12" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="E13" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" ht="12.8">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I19" s="1" t="n">
+    <row r="19" ht="74.6">
+      <c r="I19" s="1">
         <v>4</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -827,9 +913,12 @@
       <c r="K19" s="7" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I20" s="1" t="n">
+      <c r="L19" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="20" ht="13.8">
+      <c r="I20" s="1">
         <v>22</v>
       </c>
       <c r="J20" s="8" t="s">
@@ -838,9 +927,12 @@
       <c r="K20" s="9" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I21" s="1" t="n">
+      <c r="L20" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="21" ht="113.4">
+      <c r="I21" s="1">
         <v>5</v>
       </c>
       <c r="J21" s="3" t="s">
@@ -849,15 +941,18 @@
       <c r="K21" s="7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L21" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" ht="12.8">
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="1" t="n">
+      <c r="I23" s="1">
         <v>6</v>
       </c>
       <c r="J23" s="6" t="s">
@@ -866,15 +961,18 @@
       <c r="K23" s="6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L23" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" ht="12.8">
       <c r="B24" s="1" t="s">
         <v>39</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="1" t="n">
+      <c r="I24" s="1">
         <v>7</v>
       </c>
       <c r="J24" s="6" t="s">
@@ -883,8 +981,11 @@
       <c r="K24" s="6" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L24" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>39</v>
       </c>
@@ -892,13 +993,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="A27" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I28" s="1" t="n">
+    <row r="28" ht="23.85">
+      <c r="I28" s="1">
         <v>8</v>
       </c>
       <c r="J28" s="5" t="s">
@@ -907,18 +1008,21 @@
       <c r="K28" s="10" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L28" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
       <c r="B29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" ht="12.8">
       <c r="A31" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" ht="12.8">
       <c r="E32" s="1" t="s">
         <v>44</v>
       </c>
@@ -926,14 +1030,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="E33" s="1" t="s">
         <v>46</v>
       </c>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I34" s="1" t="n">
+    <row r="34" ht="64.15">
+      <c r="I34" s="1">
         <v>9</v>
       </c>
       <c r="J34" s="5" t="s">
@@ -942,8 +1046,11 @@
       <c r="K34" s="6" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L34" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" ht="13.8">
       <c r="E35" s="1" t="s">
         <v>49</v>
       </c>
@@ -953,18 +1060,18 @@
       <c r="J35" s="5"/>
       <c r="K35" s="6"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" ht="12.8">
       <c r="B36" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="A40" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="57.45">
+      <c r="I41" s="1">
         <v>10</v>
       </c>
       <c r="J41" s="5" t="s">
@@ -973,8 +1080,11 @@
       <c r="K41" s="7" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="E42" s="1" t="s">
         <v>54</v>
       </c>
@@ -982,8 +1092,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I43" s="1" t="n">
+    <row r="43" ht="91">
+      <c r="I43" s="1">
         <v>11</v>
       </c>
       <c r="J43" s="12" t="s">
@@ -992,18 +1102,21 @@
       <c r="K43" s="7" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L43" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="44" ht="12.8">
       <c r="B44" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" ht="12.8">
       <c r="A46" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" ht="12.8">
       <c r="E47" s="1" t="s">
         <v>58</v>
       </c>
@@ -1011,11 +1124,11 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" ht="12.8">
       <c r="G48" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I48" s="1" t="n">
+      <c r="I48" s="1">
         <v>12</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -1024,12 +1137,15 @@
       <c r="K48" s="9" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L48" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" ht="46.25">
       <c r="G49" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I49" s="1" t="n">
+      <c r="I49" s="1">
         <v>13</v>
       </c>
       <c r="J49" s="3" t="s">
@@ -1038,12 +1154,15 @@
       <c r="K49" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L49" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" ht="13.8">
       <c r="G50" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I50" s="1" t="n">
+      <c r="I50" s="1">
         <v>14</v>
       </c>
       <c r="J50" s="8" t="s">
@@ -1052,12 +1171,15 @@
       <c r="K50" s="9" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L50" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" ht="13.8">
       <c r="G51" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I51" s="1" t="n">
+      <c r="I51" s="1">
         <v>15</v>
       </c>
       <c r="J51" s="8" t="s">
@@ -1066,12 +1188,15 @@
       <c r="K51" s="9" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L51" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" ht="23.85">
       <c r="G52" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I52" s="1" t="n">
+      <c r="I52" s="1">
         <v>16</v>
       </c>
       <c r="J52" s="3" t="s">
@@ -1080,12 +1205,15 @@
       <c r="K52" s="9" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L52" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" ht="13.8">
       <c r="G53" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I53" s="1" t="n">
+      <c r="I53" s="1">
         <v>17</v>
       </c>
       <c r="J53" s="8" t="s">
@@ -1094,12 +1222,15 @@
       <c r="K53" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" ht="13.8">
       <c r="G54" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I54" s="1" t="n">
+      <c r="I54" s="1">
         <v>18</v>
       </c>
       <c r="J54" s="8" t="s">
@@ -1108,12 +1239,15 @@
       <c r="K54" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L54" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" ht="12.8">
       <c r="G55" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I55" s="1" t="n">
+      <c r="I55" s="1">
         <v>19</v>
       </c>
       <c r="J55" s="14" t="s">
@@ -1122,12 +1256,15 @@
       <c r="K55" s="9" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" ht="12.8">
       <c r="G56" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="I56" s="1" t="n">
+      <c r="I56" s="1">
         <v>20</v>
       </c>
       <c r="J56" s="14" t="s">
@@ -1136,14 +1273,17 @@
       <c r="K56" s="9" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" ht="12.8">
       <c r="E57" s="7"/>
       <c r="F57" s="15"/>
       <c r="G57" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I57" s="1" t="n">
+      <c r="I57" s="1">
         <v>21</v>
       </c>
       <c r="J57" s="14" t="s">
@@ -1152,11 +1292,14 @@
       <c r="K57" s="9" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L57" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" ht="12.8">
       <c r="G58" s="11"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" ht="12.8">
       <c r="E59" s="1" t="s">
         <v>58</v>
       </c>
@@ -1165,7 +1308,7 @@
       </c>
       <c r="G59" s="11"/>
     </row>
-    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" ht="12.8">
       <c r="E60" s="1" t="s">
         <v>84</v>
       </c>
@@ -1174,19 +1317,19 @@
       </c>
       <c r="G60" s="11"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" ht="12.8">
       <c r="B61" s="1" t="s">
         <v>51</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
